--- a/Bank_Results.xlsx
+++ b/Bank_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\BankParser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DFE1F5A-1E1A-402C-A3B7-CC452F072A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CBABAD-F118-4F56-9D2C-CAA47C3E23BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CE7BBC11-F063-4F4E-8401-6E769C3C185D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
   <si>
     <t xml:space="preserve">Bank Name </t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t>Multi Account /Debit Credit Row Parser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account number not getting split by ID0000 </t>
   </si>
 </sst>
 </file>
@@ -939,7 +942,12 @@
       <c r="B15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C16" s="3"/>

--- a/Bank_Results.xlsx
+++ b/Bank_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\BankParser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CBABAD-F118-4F56-9D2C-CAA47C3E23BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803116C6-BEB4-48D2-8012-51D3ABF14A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CE7BBC11-F063-4F4E-8401-6E769C3C185D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
   <si>
     <t xml:space="preserve">Bank Name </t>
   </si>
@@ -80,9 +80,6 @@
     <t xml:space="preserve">Account number not getting split by Suffix </t>
   </si>
   <si>
-    <t>Multi Account /Row Parser</t>
-  </si>
-  <si>
     <t>Mismatch in debit and interest amount ot be seperated</t>
   </si>
   <si>
@@ -152,10 +149,22 @@
     <t>Ascend Bank</t>
   </si>
   <si>
-    <t>Multi Account /Debit Credit Row Parser</t>
-  </si>
-  <si>
     <t xml:space="preserve">Account number not getting split by ID0000 </t>
+  </si>
+  <si>
+    <t>SingleMulti Account -Row Parser</t>
+  </si>
+  <si>
+    <t>Multi Account -Row Parser</t>
+  </si>
+  <si>
+    <t>Single Account -Row Parser</t>
+  </si>
+  <si>
+    <t>Single Account-Section Parser</t>
+  </si>
+  <si>
+    <t>Multi Account -Debit Credit Row Parser</t>
   </si>
 </sst>
 </file>
@@ -324,20 +333,20 @@
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>12</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>38100</xdr:rowOff>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>914400</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>320040</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1026" name="Object 2" hidden="1">
+            <xdr:cNvPr id="1027" name="Object 3" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1026"/>
+                  <a14:compatExt spid="_x0000_s1027"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{423ED2EA-47C6-5E28-2733-F21795638070}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96E64A97-65DC-3A27-121E-B3C15CDF5D0A}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -741,7 +750,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>12</v>
@@ -757,7 +766,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>8</v>
@@ -767,29 +776,29 @@
     </row>
     <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>13</v>
@@ -799,58 +808,58 @@
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
@@ -860,10 +869,10 @@
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
@@ -873,80 +882,80 @@
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1004,7 +1013,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <oleObject progId="Document" shapeId="1026" r:id="rId6">
+        <oleObject progId="Document" dvAspect="DVASPECT_ICON" shapeId="1027" r:id="rId6">
           <objectPr defaultSize="0" r:id="rId7">
             <anchor moveWithCells="1">
               <from>
@@ -1014,17 +1023,17 @@
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>12</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>30</xdr:row>
-                <xdr:rowOff>38100</xdr:rowOff>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>914400</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>320040</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
         </oleObject>
       </mc:Choice>
       <mc:Fallback>
-        <oleObject progId="Document" shapeId="1026" r:id="rId6"/>
+        <oleObject progId="Document" dvAspect="DVASPECT_ICON" shapeId="1027" r:id="rId6"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </oleObjects>

--- a/Bank_Results.xlsx
+++ b/Bank_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\BankParser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803116C6-BEB4-48D2-8012-51D3ABF14A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B9D0B2-B52A-49C8-AF83-EF5D7B7C24A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CE7BBC11-F063-4F4E-8401-6E769C3C185D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
   <si>
     <t xml:space="preserve">Bank Name </t>
   </si>
@@ -119,9 +119,6 @@
     <t>Start and End balance to be mapped correctly</t>
   </si>
   <si>
-    <t xml:space="preserve">Account number not getting split by Acc# </t>
-  </si>
-  <si>
     <t>DCU Bank</t>
   </si>
   <si>
@@ -149,9 +146,6 @@
     <t>Ascend Bank</t>
   </si>
   <si>
-    <t xml:space="preserve">Account number not getting split by ID0000 </t>
-  </si>
-  <si>
     <t>SingleMulti Account -Row Parser</t>
   </si>
   <si>
@@ -165,6 +159,18 @@
   </si>
   <si>
     <t>Multi Account -Debit Credit Row Parser</t>
+  </si>
+  <si>
+    <t>American Heritage Bank</t>
+  </si>
+  <si>
+    <t>Multi Account - Row Parser</t>
+  </si>
+  <si>
+    <t>Working fine with multi account</t>
+  </si>
+  <si>
+    <t>Account split is happening, but unknown split section also getting created which need to be corrected</t>
   </si>
 </sst>
 </file>
@@ -776,10 +782,10 @@
     </row>
     <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -792,10 +798,10 @@
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -811,7 +817,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -827,7 +833,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
@@ -843,7 +849,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
         <v>22</v>
@@ -856,10 +862,10 @@
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
@@ -869,10 +875,10 @@
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
@@ -882,10 +888,10 @@
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
@@ -898,10 +904,10 @@
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
         <v>22</v>
@@ -914,10 +920,10 @@
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
         <v>22</v>
@@ -928,38 +934,46 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
         <v>22</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
         <v>22</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C16" s="3"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C17" s="3"/>

--- a/Bank_Results.xlsx
+++ b/Bank_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\BankParser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B9D0B2-B52A-49C8-AF83-EF5D7B7C24A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44CDD00-F766-4689-88A0-2F375F1C9FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CE7BBC11-F063-4F4E-8401-6E769C3C185D}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
   <si>
     <t xml:space="preserve">Bank Name </t>
   </si>
@@ -171,6 +172,21 @@
   </si>
   <si>
     <t>Account split is happening, but unknown split section also getting created which need to be corrected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Associated Bank </t>
+  </si>
+  <si>
+    <t>Single account - Section Parser</t>
+  </si>
+  <si>
+    <t>Extracted text is getting repetition, could be issue with digitally uploaded document</t>
+  </si>
+  <si>
+    <t>Wafd Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No identifiers exists </t>
   </si>
 </sst>
 </file>
@@ -241,7 +257,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -284,7 +300,7 @@
                   <a14:compatExt spid="_x0000_s1025"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{572A6814-43F1-CEF5-5393-F34F97E11880}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -305,23 +321,10 @@
               <a:solidFill>
                 <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:miter lim="800000"/>
               <a:headEnd/>
-              <a:tailEnd type="none" w="med" len="med"/>
+              <a:tailEnd/>
             </a:ln>
-            <a:effectLst/>
-            <a:extLst>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="808080"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
-              </a:ext>
-            </a:extLst>
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
@@ -352,7 +355,7 @@
                   <a14:compatExt spid="_x0000_s1027"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96E64A97-65DC-3A27-121E-B3C15CDF5D0A}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -373,23 +376,10 @@
               <a:solidFill>
                 <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:miter lim="800000"/>
               <a:headEnd/>
-              <a:tailEnd type="none" w="med" len="med"/>
+              <a:tailEnd/>
             </a:ln>
-            <a:effectLst/>
-            <a:extLst>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="808080"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
-              </a:ext>
-            </a:extLst>
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
@@ -975,19 +965,38 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C21" s="4"/>
     </row>
   </sheetData>

--- a/Bank_Results.xlsx
+++ b/Bank_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\BankParser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44CDD00-F766-4689-88A0-2F375F1C9FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2573F767-A384-4F7A-9853-A22377820604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CE7BBC11-F063-4F4E-8401-6E769C3C185D}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
   <si>
     <t xml:space="preserve">Bank Name </t>
   </si>
@@ -75,15 +74,9 @@
     <t>Single Account /Row Parser</t>
   </si>
   <si>
-    <t>Fee to be shown separately</t>
-  </si>
-  <si>
     <t xml:space="preserve">Account number not getting split by Suffix </t>
   </si>
   <si>
-    <t>Mismatch in debit and interest amount ot be seperated</t>
-  </si>
-  <si>
     <t>Multi Account to be verified</t>
   </si>
   <si>
@@ -108,9 +101,6 @@
     <t>Working with mentioned issues</t>
   </si>
   <si>
-    <t>Debit mismatch found</t>
-  </si>
-  <si>
     <t>Debit Credit mismatch found</t>
   </si>
   <si>
@@ -168,9 +158,6 @@
     <t>Multi Account - Row Parser</t>
   </si>
   <si>
-    <t>Working fine with multi account</t>
-  </si>
-  <si>
     <t>Account split is happening, but unknown split section also getting created which need to be corrected</t>
   </si>
   <si>
@@ -186,7 +173,79 @@
     <t>Wafd Bank</t>
   </si>
   <si>
-    <t xml:space="preserve">No identifiers exists </t>
+    <t>Mountain One Bank</t>
+  </si>
+  <si>
+    <t>Empty account section getting created and checks are not read</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Fee to be shown separately and duplicate transaction</t>
+  </si>
+  <si>
+    <t>Fees is shown separate, duplicate issue not fixed</t>
+  </si>
+  <si>
+    <t>Fees showing seperately</t>
+  </si>
+  <si>
+    <t>Mismatch in debit and interest amount to be seperated</t>
+  </si>
+  <si>
+    <t>Split regex corrected and splitting happening and also empty section is removed</t>
+  </si>
+  <si>
+    <t>Checks are fixed and empty section is removed</t>
+  </si>
+  <si>
+    <t>Code fix not working</t>
+  </si>
+  <si>
+    <t>Multi account fixed, but the ID format is different between different files which is causing issue</t>
+  </si>
+  <si>
+    <t>Split regex corrected and splitting happening and also empty section is removed. Start Bal and End balance is not correct.</t>
+  </si>
+  <si>
+    <t>2 credit sections in which only one is working . May be we have to give like array.</t>
+  </si>
+  <si>
+    <t>Central Pacific Bank</t>
+  </si>
+  <si>
+    <t>Start Bal and End Balance fixed, long desc failing</t>
+  </si>
+  <si>
+    <t>New Bank</t>
+  </si>
+  <si>
+    <t>Has other transaction section which is not considered as debit or credit, hence has the mentioned issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other transactions is getting added to debit </t>
+  </si>
+  <si>
+    <t>Single account - Debit Credit Row Parser</t>
+  </si>
+  <si>
+    <t>No issues found</t>
+  </si>
+  <si>
+    <t>All the transactions are multi line</t>
+  </si>
+  <si>
+    <t>Mutli line is failing to add transactions</t>
+  </si>
+  <si>
+    <t>Single Account Row Parser</t>
+  </si>
+  <si>
+    <t>Single Account -Debit Credit Row Parser</t>
+  </si>
+  <si>
+    <t>Debit mismatch found, check without check number failing</t>
   </si>
 </sst>
 </file>
@@ -281,26 +340,26 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>4</xdr:col>
+          <xdr:col>6</xdr:col>
           <xdr:colOff>0</xdr:colOff>
           <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>922020</xdr:colOff>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>914400</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>152400</xdr:rowOff>
+          <xdr:rowOff>320040</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1025" name="Object 1" hidden="1">
+            <xdr:cNvPr id="1028" name="Object 4" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1025"/>
+                  <a14:compatExt spid="_x0000_s1028"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -336,26 +395,26 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>5</xdr:col>
+          <xdr:col>6</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>914400</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>320040</xdr:rowOff>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>922020</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>518160</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1027" name="Object 3" hidden="1">
+            <xdr:cNvPr id="1029" name="Object 5" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1027"/>
+                  <a14:compatExt spid="_x0000_s1029"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -707,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E517EF11-33F1-4688-A659-6309C2193966}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.6640625" customWidth="1"/>
@@ -716,9 +775,10 @@
     <col min="4" max="4" width="23.33203125" customWidth="1"/>
     <col min="5" max="5" width="28.5546875" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="30.109375" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -735,10 +795,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -746,15 +809,17 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -762,247 +827,298 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="F3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-    </row>
-    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-    </row>
-    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
       <c r="D8" s="5" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
+      <c r="D10" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>38</v>
       </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>41</v>
-      </c>
       <c r="B16" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>20</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
     </row>
-    <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C19" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>67</v>
+      </c>
       <c r="C21" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="E2:E14"/>
-    <mergeCell ref="F2:F14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -1011,42 +1127,17 @@
   <oleObjects>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <oleObject progId="Packager Shell Object" shapeId="1025" r:id="rId4">
+        <oleObject progId="Document" dvAspect="DVASPECT_ICON" shapeId="1028" r:id="rId4">
           <objectPr defaultSize="0" r:id="rId5">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>4</xdr:col>
+                <xdr:col>6</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
                 <xdr:row>1</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>922020</xdr:colOff>
-                <xdr:row>2</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Packager Shell Object" shapeId="1025" r:id="rId4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Document" dvAspect="DVASPECT_ICON" shapeId="1027" r:id="rId6">
-          <objectPr defaultSize="0" r:id="rId7">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>1</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>5</xdr:col>
+                <xdr:col>6</xdr:col>
                 <xdr:colOff>914400</xdr:colOff>
                 <xdr:row>2</xdr:row>
                 <xdr:rowOff>320040</xdr:rowOff>
@@ -1056,7 +1147,32 @@
         </oleObject>
       </mc:Choice>
       <mc:Fallback>
-        <oleObject progId="Document" dvAspect="DVASPECT_ICON" shapeId="1027" r:id="rId6"/>
+        <oleObject progId="Document" dvAspect="DVASPECT_ICON" shapeId="1028" r:id="rId4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Packager Shell Object" shapeId="1029" r:id="rId6">
+          <objectPr defaultSize="0" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>922020</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>518160</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Packager Shell Object" shapeId="1029" r:id="rId6"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </oleObjects>

--- a/Bank_Results.xlsx
+++ b/Bank_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\BankParser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2573F767-A384-4F7A-9853-A22377820604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD315C51-78C5-4194-B0E0-E795A5D6DC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CE7BBC11-F063-4F4E-8401-6E769C3C185D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="74">
   <si>
     <t xml:space="preserve">Bank Name </t>
   </si>
@@ -218,9 +218,6 @@
     <t>Start Bal and End Balance fixed, long desc failing</t>
   </si>
   <si>
-    <t>New Bank</t>
-  </si>
-  <si>
     <t>Has other transaction section which is not considered as debit or credit, hence has the mentioned issue</t>
   </si>
   <si>
@@ -246,13 +243,28 @@
   </si>
   <si>
     <t>Debit mismatch found, check without check number failing</t>
+  </si>
+  <si>
+    <t>Account number is in the next line which cannot be read</t>
+  </si>
+  <si>
+    <t>Canandaigua National Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Able to read transactions and check </t>
+  </si>
+  <si>
+    <t>Debit and credit not matching eventhough all transactions are read correctly</t>
+  </si>
+  <si>
+    <t>Telhio Bank</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,12 +279,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFCCCCCC"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -301,17 +307,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -766,12 +766,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E517EF11-33F1-4688-A659-6309C2193966}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.6640625" customWidth="1"/>
     <col min="2" max="2" width="21.88671875" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" style="3" customWidth="1"/>
     <col min="4" max="4" width="23.33203125" customWidth="1"/>
     <col min="5" max="5" width="28.5546875" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="30.109375" customWidth="1"/>
@@ -805,16 +805,16 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="6"/>
+      <c r="E2" s="4"/>
       <c r="F2" t="s">
         <v>49</v>
       </c>
@@ -823,16 +823,16 @@
       <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="4"/>
       <c r="F3" t="s">
         <v>50</v>
       </c>
@@ -841,31 +841,31 @@
       <c r="A4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="6"/>
+      <c r="E5" s="4"/>
       <c r="F5" t="s">
         <v>54</v>
       </c>
@@ -874,152 +874,152 @@
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="5" t="s">
+      <c r="E6" s="4"/>
+      <c r="F6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
     </row>
     <row r="7" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>68</v>
+      <c r="B7" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="6"/>
+      <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="6"/>
+      <c r="D8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="5" t="s">
+      <c r="E9" s="4"/>
+      <c r="F9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
     </row>
     <row r="10" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" s="6"/>
+      <c r="D10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="6"/>
+      <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="5" t="s">
+      <c r="E13" s="4"/>
+      <c r="F13" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="5" t="s">
+      <c r="E14" s="4"/>
+      <c r="F14" s="3" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1027,16 +1027,16 @@
       <c r="A15" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="3" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1044,16 +1044,16 @@
       <c r="A16" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="3" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1061,60 +1061,81 @@
       <c r="A17" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>63</v>
+      <c r="B19" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="5" t="s">
+    </row>
+    <row r="20" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="3"/>
-    </row>
-    <row r="21" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="4"/>
+        <v>70</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>66</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Bank_Results.xlsx
+++ b/Bank_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\BankParser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD315C51-78C5-4194-B0E0-E795A5D6DC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B853D9F0-A4CC-44E8-B082-056E8D0201FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CE7BBC11-F063-4F4E-8401-6E769C3C185D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
   <si>
     <t xml:space="preserve">Bank Name </t>
   </si>
@@ -1129,12 +1129,18 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>66</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/Bank_Results.xlsx
+++ b/Bank_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\BankParser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B853D9F0-A4CC-44E8-B082-056E8D0201FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB629AAA-296D-4A55-9A5C-8C0C1F259B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CE7BBC11-F063-4F4E-8401-6E769C3C185D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="75">
   <si>
     <t xml:space="preserve">Bank Name </t>
   </si>
@@ -258,6 +258,9 @@
   </si>
   <si>
     <t>Telhio Bank</t>
+  </si>
+  <si>
+    <t>Code fix done in section parser as it was not same as row parser.</t>
   </si>
 </sst>
 </file>
@@ -922,6 +925,10 @@
         <v>68</v>
       </c>
       <c r="E8" s="4"/>
+      <c r="F8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">

--- a/Bank_Results.xlsx
+++ b/Bank_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\BankParser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB629AAA-296D-4A55-9A5C-8C0C1F259B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7280855-63B0-450F-A007-7F2514DD9F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CE7BBC11-F063-4F4E-8401-6E769C3C185D}"/>
   </bookViews>
@@ -74,9 +74,6 @@
     <t>Single Account /Row Parser</t>
   </si>
   <si>
-    <t xml:space="preserve">Account number not getting split by Suffix </t>
-  </si>
-  <si>
     <t>Multi Account to be verified</t>
   </si>
   <si>
@@ -200,9 +197,6 @@
     <t>Checks are fixed and empty section is removed</t>
   </si>
   <si>
-    <t>Code fix not working</t>
-  </si>
-  <si>
     <t>Multi account fixed, but the ID format is different between different files which is causing issue</t>
   </si>
   <si>
@@ -261,6 +255,12 @@
   </si>
   <si>
     <t>Code fix done in section parser as it was not same as row parser.</t>
+  </si>
+  <si>
+    <t>Regex fix done and working.</t>
+  </si>
+  <si>
+    <t>Account number not getting split by Suffix . Start Bal and End Bal is not consistent</t>
   </si>
 </sst>
 </file>
@@ -798,7 +798,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
@@ -812,14 +812,14 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -830,65 +830,65 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -898,51 +898,51 @@
     </row>
     <row r="7" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -950,129 +950,129 @@
     </row>
     <row r="10" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -1080,74 +1080,74 @@
     </row>
     <row r="18" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" t="s">
         <v>62</v>
       </c>
-      <c r="C19" t="s">
-        <v>64</v>
-      </c>
       <c r="D19" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
